--- a/ops/finanzas/ARGENTINA CMC 2026 · 2 de 3 — Cómo leerlo, merch y decisiones.xlsx
+++ b/ops/finanzas/ARGENTINA CMC 2026 · 2 de 3 — Cómo leerlo, merch y decisiones.xlsx
@@ -2533,7 +2533,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>Grupo Ambient: US$13.582 por las dos propuestas</t>
+          <t>Grupo Ambient: US$14.569 por las dos propuestas</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -2542,12 +2542,12 @@
         </is>
       </c>
       <c r="D7" s="37">
-        <f>13582-33820</f>
+        <f>14569-33820</f>
         <v/>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>Cerrado. Es la mejor negociación del evento: US$20.238 por debajo de lo presupuestado.</t>
+          <t>Cerrado: 600 desayunos VIP (no 800) + comidas para 150 personas. US$19.251 por debajo de lo presupuestado. OJO: la factura 2601021 está calculada sobre 800 desayunos; pedirle a Ángeles que la reemita por 600 antes de pagar el anticipo.</t>
         </is>
       </c>
     </row>

--- a/ops/finanzas/ARGENTINA CMC 2026 · 2 de 3 — Cómo leerlo, merch y decisiones.xlsx
+++ b/ops/finanzas/ARGENTINA CMC 2026 · 2 de 3 — Cómo leerlo, merch y decisiones.xlsx
@@ -979,7 +979,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Vuelos y alojamiento del equipo entran en cero: no hay cotización ni estimado. Tampoco están cotizados los ecobaños, la marquetería, el replanteo de sillas ni los cheques, escarapelas, diplomas, placas y manillas. El costo por persona es, por lo tanto, un piso.</t>
+          <t>Esta hoja tiene sólo lo que cargó Agustina. Los ecobaños, la marquetería, el replanteo de sillas y los cheques/escarapelas/diplomas/placas/manillas están definidos pero todavía sin precio, así que entran en cero. El costo por persona es, por lo tanto, un piso.</t>
         </is>
       </c>
     </row>
